--- a/Test Upload Excel Files/TestData-Events.xlsx
+++ b/Test Upload Excel Files/TestData-Events.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Semicolon-TomorrowsVoice\Test Upload Excel Files\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E80C727-21A4-4CBD-B710-9278C7398151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="8310" yWindow="3960" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
   <si>
     <t>Name</t>
   </si>
@@ -31,33 +37,12 @@
     <t>End Time</t>
   </si>
   <si>
-    <t>Concert A</t>
-  </si>
-  <si>
-    <t>Concert B</t>
-  </si>
-  <si>
-    <t>Concert C</t>
-  </si>
-  <si>
     <t>Toronto</t>
   </si>
   <si>
-    <t>Vancouver</t>
-  </si>
-  <si>
-    <t>Montreal</t>
-  </si>
-  <si>
     <t>2025-05-10</t>
   </si>
   <si>
-    <t>2025-06-15</t>
-  </si>
-  <si>
-    <t>2025-07-20</t>
-  </si>
-  <si>
     <t>18:00</t>
   </si>
   <si>
@@ -67,20 +52,38 @@
     <t>17:30</t>
   </si>
   <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
     <t>20:30</t>
+  </si>
+  <si>
+    <t>Shelter Support</t>
+  </si>
+  <si>
+    <t>St Catharines</t>
+  </si>
+  <si>
+    <t>Charity Walk</t>
+  </si>
+  <si>
+    <t>Niagara Falls</t>
+  </si>
+  <si>
+    <t>Beach Cleanup</t>
+  </si>
+  <si>
+    <t>Senior Care Visit</t>
+  </si>
+  <si>
+    <t>Holiday Toy Drive</t>
+  </si>
+  <si>
+    <t>St. Catharines</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -132,10 +135,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -143,13 +157,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -187,7 +209,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -221,6 +243,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -255,9 +278,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -430,11 +454,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.42578125" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -451,55 +480,89 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="5">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="3">
+        <v>45823</v>
+      </c>
+      <c r="D3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="E3" s="5">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="E2" t="s">
+      <c r="C4" s="3">
+        <v>45858</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="4">
+        <v>46001</v>
+      </c>
+      <c r="D5" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="E5" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="B6" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
+      <c r="C6" s="4">
+        <v>46037</v>
+      </c>
+      <c r="D6" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="E6" s="6">
+        <v>0.66666666666666663</v>
       </c>
     </row>
   </sheetData>

--- a/Test Upload Excel Files/TestData-Events.xlsx
+++ b/Test Upload Excel Files/TestData-Events.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Semicolon-TomorrowsVoice\Test Upload Excel Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moham\Documents\Semicolon-TomorrowsVoice\Test Upload Excel Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E80C727-21A4-4CBD-B710-9278C7398151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F44A15C1-2CD2-4A88-B9F6-CAA7C058401A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8310" yWindow="3960" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t>Name</t>
   </si>
@@ -28,9 +28,6 @@
     <t>Location</t>
   </si>
   <si>
-    <t>Date</t>
-  </si>
-  <si>
     <t>Start Time</t>
   </si>
   <si>
@@ -38,9 +35,6 @@
   </si>
   <si>
     <t>Toronto</t>
-  </si>
-  <si>
-    <t>2025-05-10</t>
   </si>
   <si>
     <t>18:00</t>
@@ -135,21 +129,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -169,9 +164,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -209,9 +204,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -244,9 +239,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -279,9 +291,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -455,15 +484,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.42578125" customWidth="1"/>
     <col min="2" max="2" width="14.7109375" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -476,92 +504,74 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="C2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0.875</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D3" s="3">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="5">
-        <v>0.875</v>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3">
-        <v>45823</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="5">
-        <v>0.91666666666666663</v>
+      <c r="C5" s="5">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="3">
-        <v>45858</v>
-      </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="B6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="4">
-        <v>46001</v>
-      </c>
-      <c r="D5" s="6">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="E5" s="6">
-        <v>0.70833333333333337</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="4">
-        <v>46037</v>
-      </c>
-      <c r="D6" s="6">
+      <c r="C6" s="5">
         <v>0.5</v>
       </c>
-      <c r="E6" s="6">
+      <c r="D6" s="5">
         <v>0.66666666666666663</v>
       </c>
     </row>
